--- a/Versão5/ABNT/Ontologia_15965_3R.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_3R.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="EstaPastaDeTrabalho"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CB0F4E-A2E7-4446-BD1C-C3E2F9360833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="601" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="601" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="10" r:id="rId1"/>
@@ -3640,63 +3640,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{001CC4A1-5641-437E-9DC4-857BB9658EC6}"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <font>
         <b val="0"/>
@@ -3746,26 +3690,6 @@
         <strike val="0"/>
         <color theme="0"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4382,7 +4306,7 @@
       </c>
       <c r="B18" s="41">
         <f ca="1">NOW()</f>
-        <v>46167.413847569442</v>
+        <v>46214.346862384256</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>706</v>
@@ -5083,7 +5007,7 @@
         <v>332</v>
       </c>
       <c r="L7" s="55" t="str">
-        <f t="shared" ref="L2:N17" si="4">CONCATENATE("", C7)</f>
+        <f t="shared" ref="L7:N17" si="4">CONCATENATE("", C7)</f>
         <v>Norma</v>
       </c>
       <c r="M7" s="55" t="str">
@@ -5123,7 +5047,7 @@
         <v>723</v>
       </c>
       <c r="W7" s="58" t="str">
-        <f t="shared" ref="W2:W52" si="7">CONCATENATE("Key.ABNT.",A7)</f>
+        <f t="shared" ref="W7:W52" si="7">CONCATENATE("Key.ABNT.",A7)</f>
         <v>Key.ABNT.7</v>
       </c>
       <c r="X7" s="36" t="s">
@@ -9235,33 +9159,23 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A52">
-    <cfRule type="cellIs" dxfId="21" priority="14" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z20:AA52">
-    <cfRule type="duplicateValues" dxfId="16" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 AA7:AA19">
-    <cfRule type="cellIs" dxfId="14" priority="18" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A6">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+  <conditionalFormatting sqref="A2:A52">
+    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="Z20:AA52">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1:AA19">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9414,7 +9328,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9459,7 +9373,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34651,16 +34565,16 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:U4">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1:AA1048576">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_3R.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_3R.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0B961C-1BDB-4365-844D-0F169E583DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27410482-5C71-4073-B372-2CDEDE8B65CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="601" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8937" uniqueCount="1002">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8937" uniqueCount="1001">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -3079,9 +3079,6 @@
   </si>
   <si>
     <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
-    <t>Arquitetura</t>
   </si>
   <si>
     <t>[ 5I ]</t>
@@ -3604,63 +3601,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{001CC4A1-5641-437E-9DC4-857BB9658EC6}"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <font>
         <b val="0"/>
@@ -4326,7 +4267,7 @@
       </c>
       <c r="B18" s="39">
         <f ca="1">NOW()</f>
-        <v>46216.266402893518</v>
+        <v>46219.571610300925</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>705</v>
@@ -4431,7 +4372,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFFE5C0-D3D8-4876-B71B-E260AD929073}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA52"/>
-  <sheetFormatPr defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="6.83203125" style="30" customWidth="1"/>
@@ -4537,7 +4478,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" s="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="49">
         <v>2</v>
       </c>
@@ -4609,7 +4550,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V2" s="34" t="s">
-        <v>996</v>
+        <v>720</v>
       </c>
       <c r="W2" s="58" t="str">
         <f>CONCATENATE("Key-ABNT-",A2)</f>
@@ -4622,14 +4563,14 @@
         <v>332</v>
       </c>
       <c r="Z2" s="34" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="AA2" s="34" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" s="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="49">
         <v>3</v>
       </c>
@@ -4680,7 +4621,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="34" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="Q3" s="34" t="s">
         <v>995</v>
@@ -4701,7 +4642,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V3" s="34" t="s">
-        <v>996</v>
+        <v>720</v>
       </c>
       <c r="W3" s="58" t="str">
         <f t="shared" ref="W3:W52" si="4">CONCATENATE("Key-ABNT-",A3)</f>
@@ -4721,7 +4662,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" s="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="49">
         <v>4</v>
       </c>
@@ -4772,7 +4713,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="34" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="Q4" s="34" t="s">
         <v>995</v>
@@ -4793,7 +4734,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V4" s="34" t="s">
-        <v>996</v>
+        <v>720</v>
       </c>
       <c r="W4" s="58" t="str">
         <f t="shared" si="4"/>
@@ -4813,7 +4754,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" s="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="49">
         <v>5</v>
       </c>
@@ -4864,7 +4805,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="34" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="Q5" s="34" t="s">
         <v>995</v>
@@ -4885,7 +4826,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V5" s="34" t="s">
-        <v>996</v>
+        <v>720</v>
       </c>
       <c r="W5" s="58" t="str">
         <f t="shared" si="4"/>
@@ -4905,7 +4846,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="30" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" s="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="49">
         <v>6</v>
       </c>
@@ -4956,7 +4897,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="34" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="Q6" s="34" t="s">
         <v>995</v>
@@ -4977,7 +4918,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V6" s="34" t="s">
-        <v>996</v>
+        <v>720</v>
       </c>
       <c r="W6" s="58" t="str">
         <f t="shared" si="4"/>
@@ -4997,7 +4938,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="49">
         <v>7</v>
       </c>
@@ -5088,7 +5029,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="49">
         <v>8</v>
       </c>
@@ -5179,7 +5120,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="49">
         <v>9</v>
       </c>
@@ -5270,7 +5211,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="49">
         <v>10</v>
       </c>
@@ -5361,7 +5302,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="49">
         <v>11</v>
       </c>
@@ -5452,7 +5393,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="49">
         <v>12</v>
       </c>
@@ -5543,7 +5484,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="49">
         <v>13</v>
       </c>
@@ -5634,7 +5575,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="49">
         <v>14</v>
       </c>
@@ -5725,7 +5666,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="49">
         <v>15</v>
       </c>
@@ -5816,7 +5757,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="49">
         <v>16</v>
       </c>
@@ -5907,7 +5848,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="49">
         <v>17</v>
       </c>
@@ -5998,7 +5939,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="49">
         <v>18</v>
       </c>
@@ -6089,7 +6030,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="49">
         <v>19</v>
       </c>
@@ -6180,7 +6121,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="49">
         <v>20</v>
       </c>
@@ -6271,7 +6212,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="49">
         <v>21</v>
       </c>
@@ -6362,7 +6303,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="49">
         <v>22</v>
       </c>
@@ -6453,7 +6394,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="49">
         <v>23</v>
       </c>
@@ -6544,7 +6485,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="49">
         <v>24</v>
       </c>
@@ -6635,7 +6576,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="49">
         <v>25</v>
       </c>
@@ -6726,7 +6667,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="49">
         <v>26</v>
       </c>
@@ -6817,7 +6758,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="49">
         <v>27</v>
       </c>
@@ -6908,7 +6849,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="49">
         <v>28</v>
       </c>
@@ -6999,7 +6940,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="49">
         <v>29</v>
       </c>
@@ -7090,7 +7031,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="49">
         <v>30</v>
       </c>
@@ -7181,7 +7122,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="49">
         <v>31</v>
       </c>
@@ -7272,7 +7213,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="49">
         <v>32</v>
       </c>
@@ -7363,7 +7304,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="49">
         <v>33</v>
       </c>
@@ -7454,7 +7395,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="49">
         <v>34</v>
       </c>
@@ -7545,7 +7486,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="49">
         <v>35</v>
       </c>
@@ -7636,7 +7577,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="49">
         <v>36</v>
       </c>
@@ -7727,7 +7668,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="49">
         <v>37</v>
       </c>
@@ -7818,7 +7759,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="49">
         <v>38</v>
       </c>
@@ -7909,7 +7850,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="49">
         <v>39</v>
       </c>
@@ -8000,7 +7941,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="49">
         <v>40</v>
       </c>
@@ -8091,7 +8032,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="49">
         <v>41</v>
       </c>
@@ -8182,7 +8123,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="49">
         <v>42</v>
       </c>
@@ -8273,7 +8214,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="49">
         <v>43</v>
       </c>
@@ -8364,7 +8305,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="49">
         <v>44</v>
       </c>
@@ -8455,7 +8396,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="49">
         <v>45</v>
       </c>
@@ -8546,7 +8487,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="49">
         <v>46</v>
       </c>
@@ -8637,7 +8578,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="49">
         <v>47</v>
       </c>
@@ -8728,7 +8669,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="49">
         <v>48</v>
       </c>
@@ -8819,7 +8760,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="49">
         <v>49</v>
       </c>
@@ -8910,7 +8851,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="49">
         <v>50</v>
       </c>
@@ -9001,7 +8942,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="49">
         <v>51</v>
       </c>
@@ -9092,7 +9033,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="49">
         <v>52</v>
       </c>
@@ -9184,33 +9125,23 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A52">
-    <cfRule type="cellIs" dxfId="19" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z20:AA52">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 AA7:AA19">
-    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B52">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B6 B7:B52">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="Z20:AA52">
+    <cfRule type="duplicateValues" dxfId="8" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA1:AA19">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9363,7 +9294,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9408,7 +9339,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34600,16 +34531,16 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:U4">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1:AA1048576">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_3R.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_3R.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43324249-5D2A-495B-91E4-634F6B12588B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD68DA5-7AAF-46D4-B12C-CB1F58491E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="601" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="601" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="10" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8937" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8976" uniqueCount="1033">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -3112,13 +3112,91 @@
   </si>
   <si>
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I. Building Information Codes.</t>
+  </si>
+  <si>
+    <t>Fonte1</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>Fonte2</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>Fonte3</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>FonteVegetação1</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>FonteVegetação2</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>FonteVegetação3</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação4</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>FonteVegetação5</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>FonteVegetação6</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação7</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>FonteVegetação8</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>FonteTSB</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>FonteSINAPI</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <color theme="1"/>
@@ -3200,8 +3278,34 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Nova Cond"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3358,6 +3462,12 @@
         <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -3433,11 +3543,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3614,38 +3725,31 @@
     <xf numFmtId="0" fontId="6" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="16" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{001CC4A1-5641-437E-9DC4-857BB9658EC6}"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <font>
         <b val="0"/>
@@ -3703,6 +3807,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4108,12 +4222,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64B80B61-09F0-4F35-A733-85777283AFC6}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultColWidth="56.69921875" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.09765625" customWidth="1"/>
     <col min="2" max="2" width="65.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4311,7 +4425,7 @@
       </c>
       <c r="B18" s="39">
         <f ca="1">NOW()</f>
-        <v>46232.784326851855</v>
+        <v>46233.480766319444</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>704</v>
@@ -4407,7 +4521,157 @@
         <v>706</v>
       </c>
     </row>
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="35" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B27" s="60" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="35" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B28" s="61" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="35" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B29" s="61" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="35" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B30" s="62" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="35" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B31" s="62" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C31" s="38" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="35" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B32" s="62" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C32" s="38" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="35" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B33" s="64" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="35" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B34" s="64" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C34" s="38" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="35" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B35" s="62" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C35" s="38" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="35" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B36" s="64" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C36" s="38" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="35" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B37" s="62" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C37" s="38" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B38" s="65" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C38" s="38" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="35" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B39" s="66" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C39" s="38" t="s">
+        <v>704</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{B65DB94A-9FD0-481E-ACFE-567F7E78587E}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{BB97AE29-85BC-4D8E-8672-2601B7091FD5}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{17E93D24-F341-462D-9619-C816BDDAD755}"/>
+    <hyperlink ref="B38" r:id="rId4" xr:uid="{809F080C-D27E-4531-9A7C-C7F6C3AB2198}"/>
+    <hyperlink ref="B39" r:id="rId5" location="categoria_888" xr:uid="{8B7C460C-0518-4FEB-8276-0E127E2A6F3F}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -9169,36 +9433,26 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B6 A20:B52">
-    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
+  <conditionalFormatting sqref="A2:B52">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F19">
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z20:AA52">
-    <cfRule type="duplicateValues" dxfId="11" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA6">
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B19">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F19">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA19">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="AA1:AA19">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9351,7 +9605,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9396,7 +9650,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34588,16 +34842,16 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:U4">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1:AA1048576">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_3R.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_3R.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD68DA5-7AAF-46D4-B12C-CB1F58491E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="601" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="601" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="10" r:id="rId1"/>
@@ -4223,14 +4223,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64B80B61-09F0-4F35-A733-85777283AFC6}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="56.69921875" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="56.6640625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.09765625" customWidth="1"/>
-    <col min="2" max="2" width="65.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.3984375" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" customWidth="1"/>
+    <col min="2" max="2" width="65.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>4</v>
       </c>
@@ -4241,7 +4241,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>320</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>321</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -4274,7 +4274,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -4286,7 +4286,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
@@ -4298,7 +4298,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="7" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -4309,7 +4309,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="35" t="s">
         <v>9</v>
       </c>
@@ -4320,7 +4320,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>322</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>324</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="11" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>325</v>
       </c>
@@ -4353,7 +4353,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -4364,7 +4364,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>326</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>327</v>
       </c>
@@ -4386,7 +4386,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>328</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="16" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>329</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="17" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>12</v>
       </c>
@@ -4419,19 +4419,19 @@
         <v>704</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>330</v>
       </c>
       <c r="B18" s="39">
         <f ca="1">NOW()</f>
-        <v>46233.480766319444</v>
+        <v>46237.68528229167</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>713</v>
       </c>
@@ -4442,7 +4442,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="35" t="s">
         <v>708</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="21" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="35" t="s">
         <v>714</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="22" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="35" t="s">
         <v>319</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="23" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="35" t="s">
         <v>331</v>
       </c>
@@ -4488,7 +4488,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>336</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="25" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>338</v>
       </c>
@@ -4510,7 +4510,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="26" spans="1:3" s="40" customFormat="1" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" s="40" customFormat="1" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="35" t="s">
         <v>700</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="35" t="s">
         <v>1007</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="35" t="s">
         <v>1009</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="35" t="s">
         <v>1011</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="35" t="s">
         <v>1013</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="35" t="s">
         <v>1015</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="35" t="s">
         <v>1017</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="35" t="s">
         <v>1019</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="35" t="s">
         <v>1021</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="35" t="s">
         <v>1023</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="35" t="s">
         <v>1025</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" s="63" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="35" t="s">
         <v>1027</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>1029</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="67" customFormat="1" ht="9.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="35" t="s">
         <v>1031</v>
       </c>
@@ -4680,30 +4680,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFFE5C0-D3D8-4876-B71B-E260AD929073}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA52"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="6.796875" style="30" customWidth="1"/>
-    <col min="4" max="4" width="8.296875" style="30" customWidth="1"/>
-    <col min="5" max="5" width="8.69921875" style="30" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="6.83203125" style="30" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" style="30" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="30" customWidth="1"/>
     <col min="6" max="6" width="15" style="30" customWidth="1"/>
-    <col min="7" max="11" width="8.69921875" style="30" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.6640625" style="30" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" customWidth="1"/>
-    <col min="13" max="13" width="8.69921875" customWidth="1"/>
-    <col min="14" max="14" width="8.796875" customWidth="1"/>
-    <col min="15" max="15" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.6640625" customWidth="1"/>
+    <col min="14" max="14" width="8.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="62" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="68.19921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.796875" style="30" customWidth="1"/>
+    <col min="17" max="17" width="68.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.83203125" style="30" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="8.796875" customWidth="1"/>
+    <col min="20" max="20" width="8.83203125" customWidth="1"/>
     <col min="21" max="21" width="8.5" customWidth="1"/>
-    <col min="22" max="22" width="8.19921875" customWidth="1"/>
-    <col min="23" max="23" width="8.69921875" style="30" customWidth="1"/>
+    <col min="22" max="22" width="8.1640625" customWidth="1"/>
+    <col min="23" max="23" width="8.6640625" style="30" customWidth="1"/>
     <col min="27" max="27" width="64.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
         <v>649</v>
       </c>
@@ -4786,7 +4786,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" s="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="49">
         <v>2</v>
       </c>
@@ -4878,7 +4878,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" s="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="49">
         <v>3</v>
       </c>
@@ -4970,7 +4970,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" s="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="49">
         <v>4</v>
       </c>
@@ -5062,7 +5062,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" s="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="49">
         <v>5</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" s="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="49">
         <v>6</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="49">
         <v>7</v>
       </c>
@@ -5337,7 +5337,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="49">
         <v>8</v>
       </c>
@@ -5428,7 +5428,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="49">
         <v>9</v>
       </c>
@@ -5519,7 +5519,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="49">
         <v>10</v>
       </c>
@@ -5610,7 +5610,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="49">
         <v>11</v>
       </c>
@@ -5701,7 +5701,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="49">
         <v>12</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="49">
         <v>13</v>
       </c>
@@ -5883,7 +5883,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="49">
         <v>14</v>
       </c>
@@ -5974,7 +5974,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="49">
         <v>15</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="49">
         <v>16</v>
       </c>
@@ -6156,7 +6156,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="49">
         <v>17</v>
       </c>
@@ -6247,7 +6247,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="49">
         <v>18</v>
       </c>
@@ -6338,7 +6338,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="49">
         <v>19</v>
       </c>
@@ -6429,7 +6429,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="49">
         <v>20</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="49">
         <v>21</v>
       </c>
@@ -6611,7 +6611,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="49">
         <v>22</v>
       </c>
@@ -6702,7 +6702,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="49">
         <v>23</v>
       </c>
@@ -6793,7 +6793,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="49">
         <v>24</v>
       </c>
@@ -6884,7 +6884,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="49">
         <v>25</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="49">
         <v>26</v>
       </c>
@@ -7066,7 +7066,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="49">
         <v>27</v>
       </c>
@@ -7157,7 +7157,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="49">
         <v>28</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="49">
         <v>29</v>
       </c>
@@ -7339,7 +7339,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="49">
         <v>30</v>
       </c>
@@ -7430,7 +7430,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="49">
         <v>31</v>
       </c>
@@ -7521,7 +7521,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="49">
         <v>32</v>
       </c>
@@ -7612,7 +7612,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="49">
         <v>33</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="49">
         <v>34</v>
       </c>
@@ -7794,7 +7794,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="49">
         <v>35</v>
       </c>
@@ -7885,7 +7885,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="49">
         <v>36</v>
       </c>
@@ -7976,7 +7976,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="49">
         <v>37</v>
       </c>
@@ -8067,7 +8067,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="49">
         <v>38</v>
       </c>
@@ -8158,7 +8158,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="49">
         <v>39</v>
       </c>
@@ -8249,7 +8249,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="49">
         <v>40</v>
       </c>
@@ -8340,7 +8340,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="49">
         <v>41</v>
       </c>
@@ -8431,7 +8431,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="49">
         <v>42</v>
       </c>
@@ -8522,7 +8522,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="49">
         <v>43</v>
       </c>
@@ -8613,7 +8613,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="49">
         <v>44</v>
       </c>
@@ -8704,7 +8704,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="49">
         <v>45</v>
       </c>
@@ -8795,7 +8795,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="49">
         <v>46</v>
       </c>
@@ -8886,7 +8886,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="49">
         <v>47</v>
       </c>
@@ -8977,7 +8977,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="49">
         <v>48</v>
       </c>
@@ -9068,7 +9068,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="49">
         <v>49</v>
       </c>
@@ -9159,7 +9159,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="49">
         <v>50</v>
       </c>
@@ -9250,7 +9250,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="49">
         <v>51</v>
       </c>
@@ -9341,7 +9341,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="49">
         <v>52</v>
       </c>
@@ -9467,13 +9467,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B5591C-1220-489B-957E-6F42AD7CFACA}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
         <v>650</v>
       </c>
@@ -9538,7 +9538,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="23">
         <v>2</v>
       </c>
@@ -9620,13 +9620,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26462613-E7D7-4ABD-BD2B-4B8A0B104ED0}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="17.19921875" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="26">
         <v>1</v>
       </c>
@@ -9637,7 +9637,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="17">
         <v>2</v>
       </c>
@@ -9662,35 +9662,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4160801D-A855-4DB1-BB60-92D2B856BA2E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AA303"/>
-  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.69921875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.19921875" style="48" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.69921875" style="48" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" style="48" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="48" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.296875" style="48" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" style="48" customWidth="1"/>
     <col min="8" max="8" width="5" style="48" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.69921875" style="48" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.6640625" style="48" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5" style="48" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.19921875" style="48" customWidth="1"/>
+    <col min="11" max="11" width="9.1640625" style="48" customWidth="1"/>
     <col min="12" max="12" width="6.5" style="1" customWidth="1"/>
-    <col min="13" max="13" width="25.296875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="25.33203125" style="1" customWidth="1"/>
     <col min="14" max="14" width="7" style="48" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="82.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.796875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="82.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.83203125" style="1" customWidth="1"/>
     <col min="17" max="17" width="4.5" style="1" customWidth="1"/>
     <col min="18" max="18" width="6.5" style="1" customWidth="1"/>
     <col min="19" max="19" width="4.5" style="1" customWidth="1"/>
-    <col min="20" max="20" width="6.296875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="5.69921875" style="1" customWidth="1"/>
-    <col min="22" max="26" width="5.19921875" style="48" customWidth="1"/>
-    <col min="27" max="27" width="4.296875" style="48" customWidth="1"/>
-    <col min="28" max="16384" width="9.19921875" style="1"/>
+    <col min="20" max="20" width="6.33203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="5.6640625" style="1" customWidth="1"/>
+    <col min="22" max="26" width="5.1640625" style="48" customWidth="1"/>
+    <col min="27" max="27" width="4.33203125" style="48" customWidth="1"/>
+    <col min="28" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>333</v>
       </c>
@@ -9773,7 +9773,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -9856,7 +9856,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -9939,7 +9939,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>4</v>
       </c>
@@ -10022,7 +10022,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>5</v>
       </c>
@@ -10105,7 +10105,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>6</v>
       </c>
@@ -10188,7 +10188,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>7</v>
       </c>
@@ -10271,7 +10271,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>8</v>
       </c>
@@ -10354,7 +10354,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>9</v>
       </c>
@@ -10437,7 +10437,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>10</v>
       </c>
@@ -10520,7 +10520,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>11</v>
       </c>
@@ -10603,7 +10603,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>12</v>
       </c>
@@ -10686,7 +10686,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>13</v>
       </c>
@@ -10769,7 +10769,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>14</v>
       </c>
@@ -10852,7 +10852,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>15</v>
       </c>
@@ -10935,7 +10935,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>16</v>
       </c>
@@ -11018,7 +11018,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>17</v>
       </c>
@@ -11101,7 +11101,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>18</v>
       </c>
@@ -11184,7 +11184,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>19</v>
       </c>
@@ -11267,7 +11267,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>20</v>
       </c>
@@ -11350,7 +11350,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>21</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>22</v>
       </c>
@@ -11516,7 +11516,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>23</v>
       </c>
@@ -11599,7 +11599,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>24</v>
       </c>
@@ -11682,7 +11682,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>25</v>
       </c>
@@ -11765,7 +11765,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>26</v>
       </c>
@@ -11848,7 +11848,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>27</v>
       </c>
@@ -11931,7 +11931,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>28</v>
       </c>
@@ -12014,7 +12014,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>29</v>
       </c>
@@ -12097,7 +12097,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>30</v>
       </c>
@@ -12180,7 +12180,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>31</v>
       </c>
@@ -12263,7 +12263,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>32</v>
       </c>
@@ -12346,7 +12346,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>33</v>
       </c>
@@ -12429,7 +12429,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>34</v>
       </c>
@@ -12512,7 +12512,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>35</v>
       </c>
@@ -12595,7 +12595,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>36</v>
       </c>
@@ -12678,7 +12678,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>37</v>
       </c>
@@ -12761,7 +12761,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>38</v>
       </c>
@@ -12844,7 +12844,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>39</v>
       </c>
@@ -12927,7 +12927,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>40</v>
       </c>
@@ -13010,7 +13010,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>41</v>
       </c>
@@ -13093,7 +13093,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>42</v>
       </c>
@@ -13176,7 +13176,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>43</v>
       </c>
@@ -13259,7 +13259,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
         <v>44</v>
       </c>
@@ -13342,7 +13342,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>45</v>
       </c>
@@ -13425,7 +13425,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>46</v>
       </c>
@@ -13508,7 +13508,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>47</v>
       </c>
@@ -13591,7 +13591,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>48</v>
       </c>
@@ -13674,7 +13674,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>49</v>
       </c>
@@ -13757,7 +13757,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>50</v>
       </c>
@@ -13840,7 +13840,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>51</v>
       </c>
@@ -13923,7 +13923,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>52</v>
       </c>
@@ -14006,7 +14006,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>53</v>
       </c>
@@ -14089,7 +14089,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
         <v>54</v>
       </c>
@@ -14172,7 +14172,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>55</v>
       </c>
@@ -14255,7 +14255,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
         <v>56</v>
       </c>
@@ -14338,7 +14338,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>57</v>
       </c>
@@ -14421,7 +14421,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
         <v>58</v>
       </c>
@@ -14504,7 +14504,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>59</v>
       </c>
@@ -14587,7 +14587,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>60</v>
       </c>
@@ -14670,7 +14670,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>61</v>
       </c>
@@ -14753,7 +14753,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6">
         <v>62</v>
       </c>
@@ -14836,7 +14836,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>63</v>
       </c>
@@ -14919,7 +14919,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>64</v>
       </c>
@@ -15002,7 +15002,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>65</v>
       </c>
@@ -15085,7 +15085,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <v>66</v>
       </c>
@@ -15168,7 +15168,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <v>67</v>
       </c>
@@ -15251,7 +15251,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <v>68</v>
       </c>
@@ -15334,7 +15334,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <v>69</v>
       </c>
@@ -15417,7 +15417,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
         <v>70</v>
       </c>
@@ -15500,7 +15500,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6">
         <v>71</v>
       </c>
@@ -15583,7 +15583,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="6">
         <v>72</v>
       </c>
@@ -15666,7 +15666,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6">
         <v>73</v>
       </c>
@@ -15749,7 +15749,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="6">
         <v>74</v>
       </c>
@@ -15832,7 +15832,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6">
         <v>75</v>
       </c>
@@ -15915,7 +15915,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="6">
         <v>76</v>
       </c>
@@ -15998,7 +15998,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6">
         <v>77</v>
       </c>
@@ -16081,7 +16081,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6">
         <v>78</v>
       </c>
@@ -16164,7 +16164,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
         <v>79</v>
       </c>
@@ -16247,7 +16247,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6">
         <v>80</v>
       </c>
@@ -16330,7 +16330,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <v>81</v>
       </c>
@@ -16413,7 +16413,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <v>82</v>
       </c>
@@ -16496,7 +16496,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <v>83</v>
       </c>
@@ -16579,7 +16579,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <v>84</v>
       </c>
@@ -16662,7 +16662,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <v>85</v>
       </c>
@@ -16745,7 +16745,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <v>86</v>
       </c>
@@ -16828,7 +16828,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <v>87</v>
       </c>
@@ -16911,7 +16911,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <v>88</v>
       </c>
@@ -16994,7 +16994,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>89</v>
       </c>
@@ -17077,7 +17077,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <v>90</v>
       </c>
@@ -17160,7 +17160,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <v>91</v>
       </c>
@@ -17243,7 +17243,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <v>92</v>
       </c>
@@ -17326,7 +17326,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <v>93</v>
       </c>
@@ -17409,7 +17409,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <v>94</v>
       </c>
@@ -17492,7 +17492,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <v>95</v>
       </c>
@@ -17575,7 +17575,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="6">
         <v>96</v>
       </c>
@@ -17658,7 +17658,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="6">
         <v>97</v>
       </c>
@@ -17741,7 +17741,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="6">
         <v>98</v>
       </c>
@@ -17824,7 +17824,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="6">
         <v>99</v>
       </c>
@@ -17907,7 +17907,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="6">
         <v>100</v>
       </c>
@@ -17990,7 +17990,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="6">
         <v>101</v>
       </c>
@@ -18073,7 +18073,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="102" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="6">
         <v>102</v>
       </c>
@@ -18156,7 +18156,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="103" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="6">
         <v>103</v>
       </c>
@@ -18239,7 +18239,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="6">
         <v>104</v>
       </c>
@@ -18322,7 +18322,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="6">
         <v>105</v>
       </c>
@@ -18405,7 +18405,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="6">
         <v>106</v>
       </c>
@@ -18488,7 +18488,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="6">
         <v>107</v>
       </c>
@@ -18571,7 +18571,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="6">
         <v>108</v>
       </c>
@@ -18654,7 +18654,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6">
         <v>109</v>
       </c>
@@ -18737,7 +18737,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="6">
         <v>110</v>
       </c>
@@ -18820,7 +18820,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6">
         <v>111</v>
       </c>
@@ -18903,7 +18903,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="6">
         <v>112</v>
       </c>
@@ -18986,7 +18986,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6">
         <v>113</v>
       </c>
@@ -19069,7 +19069,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="6">
         <v>114</v>
       </c>
@@ -19152,7 +19152,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6">
         <v>115</v>
       </c>
@@ -19235,7 +19235,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="6">
         <v>116</v>
       </c>
@@ -19318,7 +19318,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="6">
         <v>117</v>
       </c>
@@ -19401,7 +19401,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="6">
         <v>118</v>
       </c>
@@ -19484,7 +19484,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="6">
         <v>119</v>
       </c>
@@ -19567,7 +19567,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="6">
         <v>120</v>
       </c>
@@ -19650,7 +19650,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="6">
         <v>121</v>
       </c>
@@ -19733,7 +19733,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="6">
         <v>122</v>
       </c>
@@ -19816,7 +19816,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="6">
         <v>123</v>
       </c>
@@ -19899,7 +19899,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="6">
         <v>124</v>
       </c>
@@ -19982,7 +19982,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="6">
         <v>125</v>
       </c>
@@ -20065,7 +20065,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="6">
         <v>126</v>
       </c>
@@ -20148,7 +20148,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="6">
         <v>127</v>
       </c>
@@ -20231,7 +20231,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="128" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="6">
         <v>128</v>
       </c>
@@ -20314,7 +20314,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="129" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="6">
         <v>129</v>
       </c>
@@ -20397,7 +20397,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="130" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="6">
         <v>130</v>
       </c>
@@ -20480,7 +20480,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="131" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="6">
         <v>131</v>
       </c>
@@ -20563,7 +20563,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="132" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="6">
         <v>132</v>
       </c>
@@ -20646,7 +20646,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="133" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="6">
         <v>133</v>
       </c>
@@ -20729,7 +20729,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="134" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="6">
         <v>134</v>
       </c>
@@ -20812,7 +20812,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="135" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="6">
         <v>135</v>
       </c>
@@ -20895,7 +20895,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="136" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="6">
         <v>136</v>
       </c>
@@ -20978,7 +20978,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="137" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="6">
         <v>137</v>
       </c>
@@ -21061,7 +21061,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="138" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="6">
         <v>138</v>
       </c>
@@ -21144,7 +21144,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="139" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="6">
         <v>139</v>
       </c>
@@ -21227,7 +21227,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="140" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="6">
         <v>140</v>
       </c>
@@ -21310,7 +21310,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="141" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="6">
         <v>141</v>
       </c>
@@ -21393,7 +21393,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="142" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="6">
         <v>142</v>
       </c>
@@ -21476,7 +21476,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="143" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="6">
         <v>143</v>
       </c>
@@ -21559,7 +21559,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="144" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="6">
         <v>144</v>
       </c>
@@ -21642,7 +21642,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="145" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="6">
         <v>145</v>
       </c>
@@ -21725,7 +21725,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="146" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="6">
         <v>146</v>
       </c>
@@ -21808,7 +21808,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="147" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="6">
         <v>147</v>
       </c>
@@ -21891,7 +21891,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="148" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="6">
         <v>148</v>
       </c>
@@ -21974,7 +21974,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="149" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="6">
         <v>149</v>
       </c>
@@ -22057,7 +22057,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="150" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="6">
         <v>150</v>
       </c>
@@ -22140,7 +22140,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="151" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="6">
         <v>151</v>
       </c>
@@ -22223,7 +22223,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="152" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="6">
         <v>152</v>
       </c>
@@ -22306,7 +22306,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="153" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="6">
         <v>153</v>
       </c>
@@ -22389,7 +22389,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="154" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="6">
         <v>154</v>
       </c>
@@ -22472,7 +22472,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="155" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="6">
         <v>155</v>
       </c>
@@ -22555,7 +22555,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="156" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="6">
         <v>156</v>
       </c>
@@ -22638,7 +22638,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="157" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="6">
         <v>157</v>
       </c>
@@ -22721,7 +22721,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="158" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="6">
         <v>158</v>
       </c>
@@ -22804,7 +22804,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="159" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="6">
         <v>159</v>
       </c>
@@ -22887,7 +22887,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="160" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="6">
         <v>160</v>
       </c>
@@ -22970,7 +22970,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="161" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="6">
         <v>161</v>
       </c>
@@ -23053,7 +23053,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="162" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="6">
         <v>162</v>
       </c>
@@ -23136,7 +23136,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="163" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="6">
         <v>163</v>
       </c>
@@ -23219,7 +23219,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="164" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="6">
         <v>164</v>
       </c>
@@ -23302,7 +23302,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="165" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="6">
         <v>165</v>
       </c>
@@ -23385,7 +23385,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="166" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="6">
         <v>166</v>
       </c>
@@ -23468,7 +23468,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="167" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="6">
         <v>167</v>
       </c>
@@ -23551,7 +23551,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="168" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="6">
         <v>168</v>
       </c>
@@ -23634,7 +23634,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="169" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="6">
         <v>169</v>
       </c>
@@ -23717,7 +23717,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="170" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="6">
         <v>170</v>
       </c>
@@ -23800,7 +23800,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="171" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="6">
         <v>171</v>
       </c>
@@ -23883,7 +23883,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="172" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="6">
         <v>172</v>
       </c>
@@ -23966,7 +23966,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="173" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="6">
         <v>173</v>
       </c>
@@ -24049,7 +24049,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="174" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="6">
         <v>174</v>
       </c>
@@ -24132,7 +24132,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="175" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="6">
         <v>175</v>
       </c>
@@ -24215,7 +24215,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="176" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="6">
         <v>176</v>
       </c>
@@ -24298,7 +24298,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="177" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="6">
         <v>177</v>
       </c>
@@ -24381,7 +24381,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="178" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="6">
         <v>178</v>
       </c>
@@ -24464,7 +24464,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="179" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="6">
         <v>179</v>
       </c>
@@ -24547,7 +24547,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="180" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="6">
         <v>180</v>
       </c>
@@ -24630,7 +24630,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="181" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="6">
         <v>181</v>
       </c>
@@ -24713,7 +24713,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="182" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="6">
         <v>182</v>
       </c>
@@ -24796,7 +24796,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="183" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="6">
         <v>183</v>
       </c>
@@ -24879,7 +24879,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="184" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="6">
         <v>184</v>
       </c>
@@ -24962,7 +24962,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="185" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="6">
         <v>185</v>
       </c>
@@ -25045,7 +25045,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="186" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="6">
         <v>186</v>
       </c>
@@ -25128,7 +25128,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="187" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="6">
         <v>187</v>
       </c>
@@ -25211,7 +25211,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="188" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="6">
         <v>188</v>
       </c>
@@ -25294,7 +25294,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="189" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="6">
         <v>189</v>
       </c>
@@ -25377,7 +25377,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="190" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="6">
         <v>190</v>
       </c>
@@ -25460,7 +25460,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="191" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="6">
         <v>191</v>
       </c>
@@ -25543,7 +25543,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="192" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="6">
         <v>192</v>
       </c>
@@ -25626,7 +25626,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="193" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="6">
         <v>193</v>
       </c>
@@ -25709,7 +25709,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="194" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="6">
         <v>194</v>
       </c>
@@ -25792,7 +25792,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="195" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="6">
         <v>195</v>
       </c>
@@ -25875,7 +25875,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="196" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="6">
         <v>196</v>
       </c>
@@ -25958,7 +25958,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="197" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="6">
         <v>197</v>
       </c>
@@ -26041,7 +26041,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="198" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="6">
         <v>198</v>
       </c>
@@ -26124,7 +26124,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="199" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="6">
         <v>199</v>
       </c>
@@ -26207,7 +26207,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="200" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="6">
         <v>200</v>
       </c>
@@ -26290,7 +26290,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="201" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="6">
         <v>201</v>
       </c>
@@ -26373,7 +26373,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="202" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="6">
         <v>202</v>
       </c>
@@ -26456,7 +26456,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="203" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="6">
         <v>203</v>
       </c>
@@ -26539,7 +26539,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="204" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="6">
         <v>204</v>
       </c>
@@ -26622,7 +26622,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="205" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="6">
         <v>205</v>
       </c>
@@ -26705,7 +26705,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="206" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="6">
         <v>206</v>
       </c>
@@ -26788,7 +26788,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="207" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="6">
         <v>207</v>
       </c>
@@ -26871,7 +26871,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="208" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="6">
         <v>208</v>
       </c>
@@ -26954,7 +26954,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="209" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="6">
         <v>209</v>
       </c>
@@ -27037,7 +27037,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="210" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="6">
         <v>210</v>
       </c>
@@ -27120,7 +27120,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="211" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="6">
         <v>211</v>
       </c>
@@ -27203,7 +27203,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="212" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="6">
         <v>212</v>
       </c>
@@ -27286,7 +27286,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="213" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="6">
         <v>213</v>
       </c>
@@ -27369,7 +27369,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="214" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="6">
         <v>214</v>
       </c>
@@ -27452,7 +27452,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="215" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="6">
         <v>215</v>
       </c>
@@ -27535,7 +27535,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="216" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="6">
         <v>216</v>
       </c>
@@ -27618,7 +27618,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="217" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="6">
         <v>217</v>
       </c>
@@ -27701,7 +27701,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="218" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="6">
         <v>218</v>
       </c>
@@ -27784,7 +27784,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="219" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="6">
         <v>219</v>
       </c>
@@ -27867,7 +27867,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="220" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="6">
         <v>220</v>
       </c>
@@ -27950,7 +27950,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="221" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="6">
         <v>221</v>
       </c>
@@ -28033,7 +28033,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="222" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="6">
         <v>222</v>
       </c>
@@ -28116,7 +28116,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="223" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="6">
         <v>223</v>
       </c>
@@ -28199,7 +28199,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="224" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="6">
         <v>224</v>
       </c>
@@ -28282,7 +28282,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="225" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="6">
         <v>225</v>
       </c>
@@ -28365,7 +28365,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="226" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="6">
         <v>226</v>
       </c>
@@ -28448,7 +28448,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="227" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="6">
         <v>227</v>
       </c>
@@ -28531,7 +28531,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="228" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="6">
         <v>228</v>
       </c>
@@ -28614,7 +28614,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="229" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="6">
         <v>229</v>
       </c>
@@ -28697,7 +28697,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="230" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="6">
         <v>230</v>
       </c>
@@ -28780,7 +28780,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="231" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="6">
         <v>231</v>
       </c>
@@ -28863,7 +28863,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="232" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="6">
         <v>232</v>
       </c>
@@ -28946,7 +28946,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="233" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="6">
         <v>233</v>
       </c>
@@ -29029,7 +29029,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="234" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="6">
         <v>234</v>
       </c>
@@ -29112,7 +29112,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="235" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="6">
         <v>235</v>
       </c>
@@ -29195,7 +29195,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="236" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="6">
         <v>236</v>
       </c>
@@ -29278,7 +29278,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="237" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="6">
         <v>237</v>
       </c>
@@ -29361,7 +29361,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="238" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="6">
         <v>238</v>
       </c>
@@ -29444,7 +29444,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="239" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="6">
         <v>239</v>
       </c>
@@ -29527,7 +29527,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="240" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="6">
         <v>240</v>
       </c>
@@ -29610,7 +29610,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="241" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="6">
         <v>241</v>
       </c>
@@ -29693,7 +29693,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="242" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="6">
         <v>242</v>
       </c>
@@ -29776,7 +29776,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="243" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="6">
         <v>243</v>
       </c>
@@ -29859,7 +29859,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="244" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="6">
         <v>244</v>
       </c>
@@ -29942,7 +29942,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="245" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="6">
         <v>245</v>
       </c>
@@ -30025,7 +30025,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="246" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="6">
         <v>246</v>
       </c>
@@ -30108,7 +30108,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="247" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="6">
         <v>247</v>
       </c>
@@ -30191,7 +30191,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="248" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="6">
         <v>248</v>
       </c>
@@ -30274,7 +30274,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="249" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="6">
         <v>249</v>
       </c>
@@ -30357,7 +30357,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="250" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="6">
         <v>250</v>
       </c>
@@ -30440,7 +30440,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="251" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="6">
         <v>251</v>
       </c>
@@ -30523,7 +30523,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="252" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="6">
         <v>252</v>
       </c>
@@ -30606,7 +30606,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="253" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="6">
         <v>253</v>
       </c>
@@ -30689,7 +30689,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="254" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="6">
         <v>254</v>
       </c>
@@ -30772,7 +30772,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="255" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="6">
         <v>255</v>
       </c>
@@ -30855,7 +30855,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="256" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="6">
         <v>256</v>
       </c>
@@ -30938,7 +30938,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="257" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="6">
         <v>257</v>
       </c>
@@ -31021,7 +31021,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="258" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="6">
         <v>258</v>
       </c>
@@ -31104,7 +31104,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="259" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="6">
         <v>259</v>
       </c>
@@ -31187,7 +31187,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="260" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="6">
         <v>260</v>
       </c>
@@ -31270,7 +31270,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="261" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="6">
         <v>261</v>
       </c>
@@ -31353,7 +31353,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="262" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="6">
         <v>262</v>
       </c>
@@ -31436,7 +31436,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="263" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="6">
         <v>263</v>
       </c>
@@ -31519,7 +31519,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="264" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="6">
         <v>264</v>
       </c>
@@ -31602,7 +31602,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="265" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="6">
         <v>265</v>
       </c>
@@ -31685,7 +31685,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="266" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="6">
         <v>266</v>
       </c>
@@ -31768,7 +31768,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="267" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="6">
         <v>267</v>
       </c>
@@ -31851,7 +31851,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="268" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="6">
         <v>268</v>
       </c>
@@ -31934,7 +31934,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="269" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="6">
         <v>269</v>
       </c>
@@ -32017,7 +32017,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="270" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="6">
         <v>270</v>
       </c>
@@ -32100,7 +32100,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="271" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="6">
         <v>271</v>
       </c>
@@ -32183,7 +32183,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="272" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="6">
         <v>272</v>
       </c>
@@ -32266,7 +32266,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="273" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="6">
         <v>273</v>
       </c>
@@ -32349,7 +32349,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="274" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="6">
         <v>274</v>
       </c>
@@ -32432,7 +32432,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="275" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="6">
         <v>275</v>
       </c>
@@ -32515,7 +32515,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="276" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="6">
         <v>276</v>
       </c>
@@ -32598,7 +32598,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="277" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="6">
         <v>277</v>
       </c>
@@ -32681,7 +32681,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="278" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="6">
         <v>278</v>
       </c>
@@ -32764,7 +32764,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="279" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="6">
         <v>279</v>
       </c>
@@ -32847,7 +32847,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="280" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="6">
         <v>280</v>
       </c>
@@ -32930,7 +32930,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="281" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="6">
         <v>281</v>
       </c>
@@ -33013,7 +33013,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="282" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="6">
         <v>282</v>
       </c>
@@ -33096,7 +33096,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="283" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="6">
         <v>283</v>
       </c>
@@ -33179,7 +33179,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="284" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="6">
         <v>284</v>
       </c>
@@ -33262,7 +33262,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="285" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="6">
         <v>285</v>
       </c>
@@ -33345,7 +33345,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="286" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="6">
         <v>286</v>
       </c>
@@ -33428,7 +33428,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="287" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="6">
         <v>287</v>
       </c>
@@ -33511,7 +33511,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="288" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="6">
         <v>288</v>
       </c>
@@ -33594,7 +33594,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="289" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="6">
         <v>289</v>
       </c>
@@ -33677,7 +33677,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="290" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="6">
         <v>290</v>
       </c>
@@ -33760,7 +33760,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="291" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="6">
         <v>291</v>
       </c>
@@ -33843,7 +33843,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="292" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="6">
         <v>292</v>
       </c>
@@ -33926,7 +33926,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="293" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="6">
         <v>293</v>
       </c>
@@ -34009,7 +34009,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="294" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="6">
         <v>294</v>
       </c>
@@ -34092,7 +34092,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="295" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="6">
         <v>295</v>
       </c>
@@ -34175,7 +34175,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="296" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="6">
         <v>296</v>
       </c>
@@ -34258,7 +34258,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="297" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="6">
         <v>297</v>
       </c>
@@ -34341,7 +34341,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="298" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="6">
         <v>298</v>
       </c>
@@ -34424,7 +34424,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="299" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="6">
         <v>299</v>
       </c>
@@ -34507,7 +34507,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="300" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="6">
         <v>300</v>
       </c>
@@ -34590,7 +34590,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="301" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="6">
         <v>301</v>
       </c>
@@ -34673,7 +34673,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="302" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="6">
         <v>302</v>
       </c>
@@ -34756,7 +34756,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="303" spans="1:27" ht="7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:27" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="6">
         <v>303</v>
       </c>
